--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>58.39396</v>
+      </c>
+      <c r="C2">
+        <v>96.23029</v>
+      </c>
+      <c r="D2">
+        <v>81.29293</v>
+      </c>
+      <c r="E2">
+        <v>49.29564</v>
+      </c>
+      <c r="F2">
         <v>58.67922</v>
       </c>
-      <c r="C2">
-        <v>58.39396</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>102.5221</v>
       </c>
-      <c r="E2">
-        <v>96.23029</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>105.4375</v>
       </c>
-      <c r="G2">
-        <v>81.29293</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>72.32344000000001</v>
-      </c>
-      <c r="I2">
-        <v>49.29564</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>54.64025</v>
+      </c>
+      <c r="C3">
+        <v>97.03292999999999</v>
+      </c>
+      <c r="D3">
+        <v>84.22732999999999</v>
+      </c>
+      <c r="E3">
+        <v>30.27594</v>
+      </c>
+      <c r="F3">
         <v>54.74453</v>
       </c>
-      <c r="C3">
-        <v>54.64025</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>102.9345</v>
       </c>
-      <c r="E3">
-        <v>97.03292999999999</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>101.8519</v>
       </c>
-      <c r="G3">
-        <v>84.22732999999999</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>44.0342</v>
-      </c>
-      <c r="I3">
-        <v>30.27594</v>
       </c>
     </row>
     <row r="4">
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>57.1116</v>
+      </c>
+      <c r="C4">
+        <v>96.14605</v>
+      </c>
+      <c r="D4">
+        <v>86.2</v>
+      </c>
+      <c r="E4">
+        <v>37.12446</v>
+      </c>
+      <c r="F4">
         <v>57.25748</v>
       </c>
-      <c r="C4">
-        <v>57.1116</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>101.9777</v>
       </c>
-      <c r="E4">
-        <v>96.14605</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>104.8</v>
       </c>
-      <c r="G4">
-        <v>86.2</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>49.8927</v>
-      </c>
-      <c r="I4">
-        <v>37.12446</v>
       </c>
     </row>
     <row r="5">
@@ -501,28 +501,28 @@
         </is>
       </c>
       <c r="B5">
+        <v>59.97151</v>
+      </c>
+      <c r="C5">
+        <v>94.63158</v>
+      </c>
+      <c r="D5">
+        <v>84.29424</v>
+      </c>
+      <c r="E5">
+        <v>22.93676</v>
+      </c>
+      <c r="F5">
         <v>60.39886</v>
       </c>
-      <c r="C5">
-        <v>59.97151</v>
-      </c>
-      <c r="D5">
+      <c r="G5">
         <v>99.47369</v>
       </c>
-      <c r="E5">
-        <v>94.63158</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>108.3499</v>
       </c>
-      <c r="G5">
-        <v>84.29424</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>32.3687</v>
-      </c>
-      <c r="I5">
-        <v>22.93676</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>52.63827</v>
+      </c>
+      <c r="C6">
+        <v>96.66414</v>
+      </c>
+      <c r="D6">
+        <v>85.05747</v>
+      </c>
+      <c r="E6">
+        <v>36.05751</v>
+      </c>
+      <c r="F6">
         <v>53.01971</v>
       </c>
-      <c r="C6">
-        <v>52.63827</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>101.6679</v>
       </c>
-      <c r="E6">
-        <v>96.66414</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>106.4233</v>
       </c>
-      <c r="G6">
-        <v>85.05747</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>50.47295</v>
-      </c>
-      <c r="I6">
-        <v>36.05751</v>
       </c>
     </row>
     <row r="7">
@@ -566,25 +566,25 @@
         <v>53.08151</v>
       </c>
       <c r="C7">
+        <v>97.36669000000001</v>
+      </c>
+      <c r="D7">
+        <v>84.65473</v>
+      </c>
+      <c r="E7">
+        <v>29.92592</v>
+      </c>
+      <c r="F7">
         <v>53.08151</v>
       </c>
-      <c r="D7">
+      <c r="G7">
         <v>104.4766</v>
       </c>
-      <c r="E7">
-        <v>97.36669000000001</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>102.8133</v>
       </c>
-      <c r="G7">
-        <v>84.65473</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>40.66667</v>
-      </c>
-      <c r="I7">
-        <v>29.92592</v>
       </c>
     </row>
     <row r="8">
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>69.64467</v>
+      </c>
+      <c r="C8">
+        <v>96.29139000000001</v>
+      </c>
+      <c r="D8">
+        <v>85.69682</v>
+      </c>
+      <c r="E8">
+        <v>37.6494</v>
+      </c>
+      <c r="F8">
         <v>69.74619</v>
       </c>
-      <c r="C8">
-        <v>69.64467</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>102.5166</v>
       </c>
-      <c r="E8">
-        <v>96.29139000000001</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>109.1687</v>
       </c>
-      <c r="G8">
-        <v>85.69682</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>55.31208</v>
-      </c>
-      <c r="I8">
-        <v>37.6494</v>
       </c>
     </row>
     <row r="9">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>56.95256</v>
+      </c>
+      <c r="C9">
+        <v>96.68763</v>
+      </c>
+      <c r="D9">
+        <v>85.08287</v>
+      </c>
+      <c r="E9">
+        <v>36.26049</v>
+      </c>
+      <c r="F9">
         <v>57.05003</v>
       </c>
-      <c r="C9">
-        <v>56.95256</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>101.6981</v>
       </c>
-      <c r="E9">
-        <v>96.68763</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>108.5423</v>
       </c>
-      <c r="G9">
-        <v>85.08287</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>52.50737</v>
-      </c>
-      <c r="I9">
-        <v>36.26049</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>62.90225</v>
+      </c>
+      <c r="C10">
+        <v>96.9173</v>
+      </c>
+      <c r="D10">
+        <v>83.97163</v>
+      </c>
+      <c r="E10">
+        <v>36.1557</v>
+      </c>
+      <c r="F10">
         <v>63.0844</v>
       </c>
-      <c r="C10">
-        <v>62.90225</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>102.4436</v>
       </c>
-      <c r="E10">
-        <v>96.9173</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>100.6383</v>
       </c>
-      <c r="G10">
-        <v>83.97163</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>50.8427</v>
-      </c>
-      <c r="I10">
-        <v>36.1557</v>
       </c>
     </row>
     <row r="11">
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>56.49484</v>
+      </c>
+      <c r="C11">
+        <v>95.72763</v>
+      </c>
+      <c r="D11">
+        <v>85.06097</v>
+      </c>
+      <c r="E11">
+        <v>32.88889</v>
+      </c>
+      <c r="F11">
         <v>56.70103</v>
       </c>
-      <c r="C11">
-        <v>56.49484</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>100.6676</v>
       </c>
-      <c r="E11">
-        <v>95.72763</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>100.9146</v>
       </c>
-      <c r="G11">
-        <v>85.06097</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>45.03704</v>
-      </c>
-      <c r="I11">
-        <v>32.88889</v>
       </c>
     </row>
     <row r="12">
@@ -721,25 +721,25 @@
         <v>62.15853</v>
       </c>
       <c r="C12">
+        <v>96.45834000000001</v>
+      </c>
+      <c r="D12">
+        <v>81.87222</v>
+      </c>
+      <c r="E12">
+        <v>38.40934</v>
+      </c>
+      <c r="F12">
         <v>62.15853</v>
       </c>
-      <c r="D12">
+      <c r="G12">
         <v>103.0208</v>
       </c>
-      <c r="E12">
-        <v>96.45834000000001</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>105.3987</v>
       </c>
-      <c r="G12">
-        <v>81.87222</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>54.77742</v>
-      </c>
-      <c r="I12">
-        <v>38.40934</v>
       </c>
     </row>
     <row r="13">
@@ -749,28 +749,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>56.03139</v>
+      </c>
+      <c r="C13">
+        <v>96.90688</v>
+      </c>
+      <c r="D13">
+        <v>83.0461</v>
+      </c>
+      <c r="E13">
+        <v>37.24701</v>
+      </c>
+      <c r="F13">
         <v>56.21907</v>
       </c>
-      <c r="C13">
-        <v>56.03139</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>103.5319</v>
       </c>
-      <c r="E13">
-        <v>96.90688</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>109.414</v>
       </c>
-      <c r="G13">
-        <v>83.0461</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>54.77231</v>
-      </c>
-      <c r="I13">
-        <v>37.24701</v>
       </c>
     </row>
     <row r="14">
@@ -783,25 +783,25 @@
         <v>59.52813</v>
       </c>
       <c r="C14">
+        <v>95.62044</v>
+      </c>
+      <c r="D14">
+        <v>81.03045</v>
+      </c>
+      <c r="E14">
+        <v>30.47493</v>
+      </c>
+      <c r="F14">
         <v>59.52813</v>
       </c>
-      <c r="D14">
+      <c r="G14">
         <v>102.4331</v>
       </c>
-      <c r="E14">
-        <v>95.62044</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>106.089</v>
       </c>
-      <c r="G14">
-        <v>81.03045</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>45.51451</v>
-      </c>
-      <c r="I14">
-        <v>30.47493</v>
       </c>
     </row>
     <row r="15">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="B15">
+        <v>63.45382</v>
+      </c>
+      <c r="C15">
+        <v>97.00621</v>
+      </c>
+      <c r="D15">
+        <v>86.2423</v>
+      </c>
+      <c r="E15">
+        <v>38.35139</v>
+      </c>
+      <c r="F15">
         <v>63.56856</v>
       </c>
-      <c r="C15">
-        <v>63.45382</v>
-      </c>
-      <c r="D15">
+      <c r="G15">
         <v>102.1176</v>
       </c>
-      <c r="E15">
-        <v>97.00621</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>101.7796</v>
       </c>
-      <c r="G15">
-        <v>86.2423</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>56.50155</v>
-      </c>
-      <c r="I15">
-        <v>38.35139</v>
       </c>
     </row>
     <row r="16">
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="B16">
+        <v>49.596</v>
+      </c>
+      <c r="C16">
+        <v>93.25512999999999</v>
+      </c>
+      <c r="D16">
+        <v>84.60674</v>
+      </c>
+      <c r="E16">
+        <v>31.84109</v>
+      </c>
+      <c r="F16">
         <v>49.86533</v>
       </c>
-      <c r="C16">
-        <v>49.596</v>
-      </c>
-      <c r="D16">
+      <c r="G16">
         <v>97.44868</v>
       </c>
-      <c r="E16">
-        <v>93.25512999999999</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>100.7865</v>
       </c>
-      <c r="G16">
-        <v>84.60674</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>43.07738</v>
-      </c>
-      <c r="I16">
-        <v>31.84109</v>
       </c>
     </row>
     <row r="17">
@@ -873,28 +873,28 @@
         </is>
       </c>
       <c r="B17">
+        <v>48.44587</v>
+      </c>
+      <c r="C17">
+        <v>96.76331999999999</v>
+      </c>
+      <c r="D17">
+        <v>87.01987</v>
+      </c>
+      <c r="E17">
+        <v>26.12613</v>
+      </c>
+      <c r="F17">
         <v>48.55305</v>
       </c>
-      <c r="C17">
-        <v>48.44587</v>
-      </c>
-      <c r="D17">
+      <c r="G17">
         <v>103.3715</v>
       </c>
-      <c r="E17">
-        <v>96.76331999999999</v>
-      </c>
-      <c r="F17">
+      <c r="H17">
         <v>104.7682</v>
       </c>
-      <c r="G17">
-        <v>87.01987</v>
-      </c>
-      <c r="H17">
+      <c r="I17">
         <v>35.38084</v>
-      </c>
-      <c r="I17">
-        <v>26.12613</v>
       </c>
     </row>
     <row r="18">
@@ -907,25 +907,25 @@
         <v>54.34381</v>
       </c>
       <c r="C18">
+        <v>97.12945999999999</v>
+      </c>
+      <c r="D18">
+        <v>86.98031</v>
+      </c>
+      <c r="E18">
+        <v>30.94595</v>
+      </c>
+      <c r="F18">
         <v>54.34381</v>
       </c>
-      <c r="D18">
+      <c r="G18">
         <v>102.812</v>
       </c>
-      <c r="E18">
-        <v>97.12945999999999</v>
-      </c>
-      <c r="F18">
+      <c r="H18">
         <v>99.12473</v>
       </c>
-      <c r="G18">
-        <v>86.98031</v>
-      </c>
-      <c r="H18">
+      <c r="I18">
         <v>40.94595</v>
-      </c>
-      <c r="I18">
-        <v>30.94595</v>
       </c>
     </row>
     <row r="19">
@@ -938,25 +938,25 @@
         <v>62.20472</v>
       </c>
       <c r="C19">
+        <v>96.99381</v>
+      </c>
+      <c r="D19">
+        <v>89.48193999999999</v>
+      </c>
+      <c r="E19">
+        <v>34.34343</v>
+      </c>
+      <c r="F19">
         <v>62.20472</v>
       </c>
-      <c r="D19">
+      <c r="G19">
         <v>101.6799</v>
       </c>
-      <c r="E19">
-        <v>96.99381</v>
-      </c>
-      <c r="F19">
+      <c r="H19">
         <v>108.0063</v>
       </c>
-      <c r="G19">
-        <v>89.48193999999999</v>
-      </c>
-      <c r="H19">
+      <c r="I19">
         <v>49.59596</v>
-      </c>
-      <c r="I19">
-        <v>34.34343</v>
       </c>
     </row>
     <row r="20">
@@ -966,28 +966,28 @@
         </is>
       </c>
       <c r="B20">
+        <v>57.57851</v>
+      </c>
+      <c r="C20">
+        <v>97.10059</v>
+      </c>
+      <c r="D20">
+        <v>83.47978999999999</v>
+      </c>
+      <c r="E20">
+        <v>34.41579</v>
+      </c>
+      <c r="F20">
         <v>57.71507</v>
       </c>
-      <c r="C20">
-        <v>57.57851</v>
-      </c>
-      <c r="D20">
+      <c r="G20">
         <v>102.7219</v>
       </c>
-      <c r="E20">
-        <v>97.10059</v>
-      </c>
-      <c r="F20">
+      <c r="H20">
         <v>103.2806</v>
       </c>
-      <c r="G20">
-        <v>83.47978999999999</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>49.28367</v>
-      </c>
-      <c r="I20">
-        <v>34.41579</v>
       </c>
     </row>
     <row r="21">
@@ -997,28 +997,28 @@
         </is>
       </c>
       <c r="B21">
+        <v>58.23293</v>
+      </c>
+      <c r="C21">
+        <v>96.01022</v>
+      </c>
+      <c r="D21">
+        <v>87.27819</v>
+      </c>
+      <c r="E21">
+        <v>35.36346</v>
+      </c>
+      <c r="F21">
         <v>58.61446</v>
       </c>
-      <c r="C21">
-        <v>58.23293</v>
-      </c>
-      <c r="D21">
+      <c r="G21">
         <v>100.4686</v>
       </c>
-      <c r="E21">
-        <v>96.01022</v>
-      </c>
-      <c r="F21">
+      <c r="H21">
         <v>104.368</v>
       </c>
-      <c r="G21">
-        <v>87.27819</v>
-      </c>
-      <c r="H21">
+      <c r="I21">
         <v>48.2545</v>
-      </c>
-      <c r="I21">
-        <v>35.36346</v>
       </c>
     </row>
     <row r="22">
@@ -1031,25 +1031,25 @@
         <v>56.42292</v>
       </c>
       <c r="C22">
+        <v>97.12643</v>
+      </c>
+      <c r="D22">
+        <v>82.44746000000001</v>
+      </c>
+      <c r="E22">
+        <v>30.75697</v>
+      </c>
+      <c r="F22">
         <v>56.42292</v>
       </c>
-      <c r="D22">
+      <c r="G22">
         <v>103.6398</v>
       </c>
-      <c r="E22">
-        <v>97.12643</v>
-      </c>
-      <c r="F22">
+      <c r="H22">
         <v>100.1236</v>
       </c>
-      <c r="G22">
-        <v>82.44746000000001</v>
-      </c>
-      <c r="H22">
+      <c r="I22">
         <v>44.38247</v>
-      </c>
-      <c r="I22">
-        <v>30.75697</v>
       </c>
     </row>
     <row r="23">
@@ -1059,28 +1059,28 @@
         </is>
       </c>
       <c r="B23">
+        <v>64.62851999999999</v>
+      </c>
+      <c r="C23">
+        <v>96.40392</v>
+      </c>
+      <c r="D23">
+        <v>85.87132</v>
+      </c>
+      <c r="E23">
+        <v>34.78766</v>
+      </c>
+      <c r="F23">
         <v>64.88232000000001</v>
       </c>
-      <c r="C23">
-        <v>64.62851999999999</v>
-      </c>
-      <c r="D23">
+      <c r="G23">
         <v>100.7064</v>
       </c>
-      <c r="E23">
-        <v>96.40392</v>
-      </c>
-      <c r="F23">
+      <c r="H23">
         <v>107.7595</v>
       </c>
-      <c r="G23">
-        <v>85.87132</v>
-      </c>
-      <c r="H23">
+      <c r="I23">
         <v>51.12807</v>
-      </c>
-      <c r="I23">
-        <v>34.78766</v>
       </c>
     </row>
     <row r="24">
@@ -1090,28 +1090,28 @@
         </is>
       </c>
       <c r="B24">
+        <v>60.63158</v>
+      </c>
+      <c r="C24">
+        <v>96.86113</v>
+      </c>
+      <c r="D24">
+        <v>83.60760000000001</v>
+      </c>
+      <c r="E24">
+        <v>28.95534</v>
+      </c>
+      <c r="F24">
         <v>60.68421</v>
       </c>
-      <c r="C24">
-        <v>60.63158</v>
-      </c>
-      <c r="D24">
+      <c r="G24">
         <v>102.2511</v>
       </c>
-      <c r="E24">
-        <v>96.86113</v>
-      </c>
-      <c r="F24">
+      <c r="H24">
         <v>101.962</v>
       </c>
-      <c r="G24">
-        <v>83.60760000000001</v>
-      </c>
-      <c r="H24">
+      <c r="I24">
         <v>41.71083</v>
-      </c>
-      <c r="I24">
-        <v>28.95534</v>
       </c>
     </row>
     <row r="25">
@@ -1124,25 +1124,25 @@
         <v>62.95181</v>
       </c>
       <c r="C25">
+        <v>95.97523</v>
+      </c>
+      <c r="D25">
+        <v>84.94846</v>
+      </c>
+      <c r="E25">
+        <v>33.125</v>
+      </c>
+      <c r="F25">
         <v>62.95181</v>
       </c>
-      <c r="D25">
+      <c r="G25">
         <v>101.4448</v>
       </c>
-      <c r="E25">
-        <v>95.97523</v>
-      </c>
-      <c r="F25">
+      <c r="H25">
         <v>98.14433</v>
       </c>
-      <c r="G25">
-        <v>84.94846</v>
-      </c>
-      <c r="H25">
+      <c r="I25">
         <v>47.5</v>
-      </c>
-      <c r="I25">
-        <v>33.125</v>
       </c>
     </row>
     <row r="26">
@@ -1155,25 +1155,25 @@
         <v>60.33163</v>
       </c>
       <c r="C26">
+        <v>96.16027</v>
+      </c>
+      <c r="D26">
+        <v>81.01472</v>
+      </c>
+      <c r="E26">
+        <v>22.92733</v>
+      </c>
+      <c r="F26">
         <v>60.33163</v>
       </c>
-      <c r="D26">
+      <c r="G26">
         <v>103.6728</v>
       </c>
-      <c r="E26">
-        <v>96.16027</v>
-      </c>
-      <c r="F26">
+      <c r="H26">
         <v>97.05401000000001</v>
       </c>
-      <c r="G26">
-        <v>81.01472</v>
-      </c>
-      <c r="H26">
+      <c r="I26">
         <v>32.85568</v>
-      </c>
-      <c r="I26">
-        <v>22.92733</v>
       </c>
     </row>
     <row r="27">
@@ -1183,28 +1183,28 @@
         </is>
       </c>
       <c r="B27">
+        <v>51.33877</v>
+      </c>
+      <c r="C27">
+        <v>96.13601</v>
+      </c>
+      <c r="D27">
+        <v>81.81818</v>
+      </c>
+      <c r="E27">
+        <v>24.16667</v>
+      </c>
+      <c r="F27">
         <v>51.33876</v>
       </c>
-      <c r="C27">
-        <v>51.33877</v>
-      </c>
-      <c r="D27">
+      <c r="G27">
         <v>102.473</v>
       </c>
-      <c r="E27">
-        <v>96.13601</v>
-      </c>
-      <c r="F27">
+      <c r="H27">
         <v>94.94949</v>
       </c>
-      <c r="G27">
-        <v>81.81818</v>
-      </c>
-      <c r="H27">
+      <c r="I27">
         <v>31.83333</v>
-      </c>
-      <c r="I27">
-        <v>24.16667</v>
       </c>
     </row>
     <row r="28">
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="B28">
+        <v>65.58044</v>
+      </c>
+      <c r="C28">
+        <v>97.67442</v>
+      </c>
+      <c r="D28">
+        <v>84.67153</v>
+      </c>
+      <c r="E28">
+        <v>27.99462</v>
+      </c>
+      <c r="F28">
         <v>65.78411</v>
       </c>
-      <c r="C28">
-        <v>65.58044</v>
-      </c>
-      <c r="D28">
+      <c r="G28">
         <v>103.9168</v>
       </c>
-      <c r="E28">
-        <v>97.67442</v>
-      </c>
-      <c r="F28">
+      <c r="H28">
         <v>98.54015</v>
       </c>
-      <c r="G28">
-        <v>84.67153</v>
-      </c>
-      <c r="H28">
+      <c r="I28">
         <v>38.62719</v>
-      </c>
-      <c r="I28">
-        <v>27.99462</v>
       </c>
     </row>
     <row r="29">
@@ -1248,25 +1248,25 @@
         <v>55.48961</v>
       </c>
       <c r="C29">
+        <v>98.48054</v>
+      </c>
+      <c r="D29">
+        <v>79.59184</v>
+      </c>
+      <c r="E29">
+        <v>25.57905</v>
+      </c>
+      <c r="F29">
         <v>55.48961</v>
       </c>
-      <c r="D29">
+      <c r="G29">
         <v>109.2118</v>
       </c>
-      <c r="E29">
-        <v>98.48054</v>
-      </c>
-      <c r="F29">
+      <c r="H29">
         <v>92.57885</v>
       </c>
-      <c r="G29">
-        <v>79.59184</v>
-      </c>
-      <c r="H29">
+      <c r="I29">
         <v>33.73615</v>
-      </c>
-      <c r="I29">
-        <v>25.57905</v>
       </c>
     </row>
     <row r="30">
@@ -1276,28 +1276,28 @@
         </is>
       </c>
       <c r="B30">
+        <v>64.95177</v>
+      </c>
+      <c r="C30">
+        <v>96.9697</v>
+      </c>
+      <c r="D30">
+        <v>81.72942999999999</v>
+      </c>
+      <c r="E30">
+        <v>33.28358</v>
+      </c>
+      <c r="F30">
         <v>65.05895</v>
       </c>
-      <c r="C30">
-        <v>64.95177</v>
-      </c>
-      <c r="D30">
+      <c r="G30">
         <v>103.7037</v>
       </c>
-      <c r="E30">
-        <v>96.9697</v>
-      </c>
-      <c r="F30">
+      <c r="H30">
         <v>98.74477</v>
       </c>
-      <c r="G30">
-        <v>81.72942999999999</v>
-      </c>
-      <c r="H30">
+      <c r="I30">
         <v>45.22388</v>
-      </c>
-      <c r="I30">
-        <v>33.28358</v>
       </c>
     </row>
     <row r="31">
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="B31">
+        <v>62.13018</v>
+      </c>
+      <c r="C31">
+        <v>96.51163</v>
+      </c>
+      <c r="D31">
+        <v>81.99357000000001</v>
+      </c>
+      <c r="E31">
+        <v>33.82762</v>
+      </c>
+      <c r="F31">
         <v>62.36686</v>
       </c>
-      <c r="C31">
-        <v>62.13018</v>
-      </c>
-      <c r="D31">
+      <c r="G31">
         <v>101.9103</v>
       </c>
-      <c r="E31">
-        <v>96.51163</v>
-      </c>
-      <c r="F31">
+      <c r="H31">
         <v>99.67846</v>
       </c>
-      <c r="G31">
-        <v>81.99357000000001</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>48.28545</v>
-      </c>
-      <c r="I31">
-        <v>33.82762</v>
       </c>
     </row>
     <row r="32">
@@ -1338,28 +1338,28 @@
         </is>
       </c>
       <c r="B32">
+        <v>63.5675</v>
+      </c>
+      <c r="C32">
+        <v>97.24075999999999</v>
+      </c>
+      <c r="D32">
+        <v>79.46274</v>
+      </c>
+      <c r="E32">
+        <v>31.66081</v>
+      </c>
+      <c r="F32">
         <v>63.56749</v>
       </c>
-      <c r="C32">
-        <v>63.5675</v>
-      </c>
-      <c r="D32">
+      <c r="G32">
         <v>105.6965</v>
       </c>
-      <c r="E32">
-        <v>97.24075999999999</v>
-      </c>
-      <c r="F32">
+      <c r="H32">
         <v>107.0191</v>
       </c>
-      <c r="G32">
-        <v>79.46274</v>
-      </c>
-      <c r="H32">
+      <c r="I32">
         <v>45.45911</v>
-      </c>
-      <c r="I32">
-        <v>31.66081</v>
       </c>
     </row>
     <row r="33">
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="B33">
+        <v>61.79993</v>
+      </c>
+      <c r="C33">
+        <v>96.87148000000001</v>
+      </c>
+      <c r="D33">
+        <v>83.49007</v>
+      </c>
+      <c r="E33">
+        <v>38.62854</v>
+      </c>
+      <c r="F33">
         <v>61.87717</v>
       </c>
-      <c r="C33">
-        <v>61.79993</v>
-      </c>
-      <c r="D33">
+      <c r="G33">
         <v>103.1003</v>
       </c>
-      <c r="E33">
-        <v>96.87148000000001</v>
-      </c>
-      <c r="F33">
+      <c r="H33">
         <v>105.2247</v>
       </c>
-      <c r="G33">
-        <v>83.49007</v>
-      </c>
-      <c r="H33">
+      <c r="I33">
         <v>56.7911</v>
-      </c>
-      <c r="I33">
-        <v>38.62854</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:39</t>
+    <t xml:space="preserve">2026-08-02 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:39</t>
+    <t xml:space="preserve">2026-08-05 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:32</t>
+    <t xml:space="preserve">2026-08-05 18:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 18:14</t>
+    <t xml:space="preserve">2026-08-16 09:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:44</t>
+    <t xml:space="preserve">2026-08-19 11:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:39</t>
+    <t xml:space="preserve">2026-08-28 11:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:21</t>
+    <t xml:space="preserve">2026-09-06 17:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
